--- a/src/results_template/CEC2020/20Dim.xlsx
+++ b/src/results_template/CEC2020/20Dim.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\Research\Project Test\Base-Optimization-Framework\src\results_template\CEC2020\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\Research\Project Test\src\results_template\CEC2020\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{3FA1448B-0DCF-424C-ACB0-B553BBE09C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCFB52EA-8BD4-4113-9C72-216BFB1FAADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conclusions" sheetId="1" r:id="rId1"/>
@@ -22,20 +22,8 @@
     <sheet name="Friedman" sheetId="7" r:id="rId7"/>
     <sheet name="Explanation" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -44,12 +32,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="101">
   <si>
     <t>Comparison of optimization results for the CEC benchmark functions 2020 (20 Dim)</t>
   </si>
   <si>
     <t>Functions</t>
+  </si>
+  <si>
+    <t>Algorithm 1</t>
+  </si>
+  <si>
+    <t>Algorithm 2</t>
+  </si>
+  <si>
+    <t>Algorithm 3</t>
+  </si>
+  <si>
+    <t>Algorithm 4</t>
+  </si>
+  <si>
+    <t>Algorithm 5</t>
+  </si>
+  <si>
+    <t>Algorithm 6</t>
+  </si>
+  <si>
+    <t>Algorithm 7</t>
+  </si>
+  <si>
+    <t>Algorithm 8</t>
+  </si>
+  <si>
+    <t>Algorithm 9</t>
+  </si>
+  <si>
+    <t>Algorithm 10</t>
+  </si>
+  <si>
+    <t>Algorithm 11</t>
+  </si>
+  <si>
+    <t>Algorithm 12</t>
+  </si>
+  <si>
+    <t>Algorithm 13</t>
+  </si>
+  <si>
+    <t>Algorithm 14</t>
+  </si>
+  <si>
+    <t>Algorithm 15</t>
   </si>
   <si>
     <t>Unimodal
@@ -107,177 +140,129 @@
     <t>F10</t>
   </si>
   <si>
-    <t>Algorithm 1</t>
-  </si>
-  <si>
-    <t>Algorithm 2</t>
-  </si>
-  <si>
-    <t>Algorithm 3</t>
-  </si>
-  <si>
-    <t>Algorithm 4</t>
-  </si>
-  <si>
-    <t>Algorithm 5</t>
-  </si>
-  <si>
-    <t>Algorithm 6</t>
-  </si>
-  <si>
-    <t>Algorithm 7</t>
-  </si>
-  <si>
-    <t>Algorithm 8</t>
-  </si>
-  <si>
-    <t>Algorithm 9</t>
-  </si>
-  <si>
-    <t>Algorithm 10</t>
-  </si>
-  <si>
-    <t>Algorithm 11</t>
-  </si>
-  <si>
-    <t>Algorithm 12</t>
-  </si>
-  <si>
-    <t>Algorithm 13</t>
-  </si>
-  <si>
-    <t>Algorithm 14</t>
-  </si>
-  <si>
-    <t>Algorithm 15</t>
-  </si>
-  <si>
-    <t>Number of Best Functions</t>
+    <t>P-value of the one-sided Welch t-test for the CEC benchmark functions 2020 (20 Dim)</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>alg_base vs alg2</t>
+  </si>
+  <si>
+    <t>alg_base vs alg3</t>
+  </si>
+  <si>
+    <t>alg_base vs alg4</t>
+  </si>
+  <si>
+    <t>alg_base vs alg5</t>
+  </si>
+  <si>
+    <t>alg_base vs alg6</t>
+  </si>
+  <si>
+    <t>alg_base vs alg7</t>
+  </si>
+  <si>
+    <t>alg_base vs alg8</t>
+  </si>
+  <si>
+    <t>alg_base vs alg9</t>
+  </si>
+  <si>
+    <t>alg_base vs alg10</t>
+  </si>
+  <si>
+    <t>alg_base vs alg11</t>
+  </si>
+  <si>
+    <t>alg_base vs alg12</t>
+  </si>
+  <si>
+    <t>alg_base vs alg13</t>
+  </si>
+  <si>
+    <t>alg_base vs alg14</t>
+  </si>
+  <si>
+    <t>alg_base vs alg15</t>
+  </si>
+  <si>
+    <t>Decision (h) of the one-sided Welch t-test for the CEC benchmark functions 2020 (20 Dim)</t>
+  </si>
+  <si>
+    <t>P-value of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2020 (20 Dim)</t>
+  </si>
+  <si>
+    <t>Decision (h) of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2020 (20 Dim)</t>
+  </si>
+  <si>
+    <t>Rank-sum statistic (W) for the Wilcoxon rank-sum test for the CEC benchmark functions 2020 (20 Dim)</t>
+  </si>
+  <si>
+    <t>Function ranking and overall Friedman analysis for the CEC benchmark functions 2020 (20 Dim)</t>
+  </si>
+  <si>
+    <t>Algorithm 1 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 2 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 3 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 4 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 5 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 6 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 7 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 8 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 9 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 10 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 11 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 12 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 13 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 14 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 15 Rank</t>
+  </si>
+  <si>
+    <t>Best Algorithm</t>
+  </si>
+  <si>
+    <t>Kruskal-Wallis p</t>
+  </si>
+  <si>
+    <t>Significant?</t>
+  </si>
+  <si>
+    <t>Average Rank</t>
   </si>
   <si>
     <t>Overall Rank</t>
   </si>
   <si>
-    <t>P-value of the one-sided Welch t-test for the CEC benchmark functions 2020 (20 Dim)</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>alg_base vs alg2</t>
-  </si>
-  <si>
-    <t>alg_base vs alg3</t>
-  </si>
-  <si>
-    <t>alg_base vs alg4</t>
-  </si>
-  <si>
-    <t>alg_base vs alg5</t>
-  </si>
-  <si>
-    <t>alg_base vs alg6</t>
-  </si>
-  <si>
-    <t>alg_base vs alg7</t>
-  </si>
-  <si>
-    <t>alg_base vs alg8</t>
-  </si>
-  <si>
-    <t>alg_base vs alg9</t>
-  </si>
-  <si>
-    <t>alg_base vs alg10</t>
-  </si>
-  <si>
-    <t>alg_base vs alg11</t>
-  </si>
-  <si>
-    <t>alg_base vs alg12</t>
-  </si>
-  <si>
-    <t>alg_base vs alg13</t>
-  </si>
-  <si>
-    <t>alg_base vs alg14</t>
-  </si>
-  <si>
-    <t>alg_base vs alg15</t>
-  </si>
-  <si>
-    <t>Decision (h) of the one-sided Welch t-test for the CEC benchmark functions 2020 (20 Dim)</t>
-  </si>
-  <si>
-    <t>P-value of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2020 (20 Dim)</t>
-  </si>
-  <si>
-    <t>Decision (h) of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2020 (20 Dim)</t>
-  </si>
-  <si>
-    <t>Rank-sum statistic (W) for the Wilcoxon rank-sum test for the CEC benchmark functions 2020 (20 Dim)</t>
-  </si>
-  <si>
-    <t>Function ranking and overall Friedman analysis for the CEC benchmark functions 2020 (20 Dim)</t>
-  </si>
-  <si>
-    <t>Algorithm 1 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 2 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 3 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 4 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 5 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 6 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 7 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 8 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 9 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 10 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 11 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 12 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 13 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 14 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 15 Rank</t>
-  </si>
-  <si>
-    <t>Best Algorithm</t>
-  </si>
-  <si>
-    <t>Kruskal-Wallis p</t>
-  </si>
-  <si>
-    <t>Significant?</t>
-  </si>
-  <si>
-    <t>Average Rank</t>
-  </si>
-  <si>
     <t>Overall Friedman Test</t>
   </si>
   <si>
@@ -348,6 +333,12 @@
   </si>
   <si>
     <t>Optional figures showing the distribution of final objective values across independent runs for each function and algorithm.</t>
+  </si>
+  <si>
+    <t>Total number of best answers</t>
+  </si>
+  <si>
+    <t>Total number of equal-best answers</t>
   </si>
 </sst>
 </file>
@@ -484,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -529,7 +520,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -545,23 +535,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -569,14 +544,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -723,9 +720,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -830,99 +827,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R34"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.109375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" style="6" customWidth="1"/>
     <col min="2" max="2" width="4" style="6" customWidth="1"/>
     <col min="3" max="3" width="6" style="6" customWidth="1"/>
-    <col min="4" max="12" width="11.33203125" style="6" customWidth="1"/>
-    <col min="13" max="18" width="12.33203125" style="6" customWidth="1"/>
-    <col min="19" max="16384" width="8.88671875" style="6"/>
+    <col min="4" max="12" width="11.28515625" style="6" customWidth="1"/>
+    <col min="13" max="18" width="12.28515625" style="6" customWidth="1"/>
+    <col min="19" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+    </row>
+    <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -940,13 +937,11 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="26"/>
-      <c r="B4" s="8" t="s">
-        <v>3</v>
-      </c>
+    <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="32"/>
+      <c r="B4" s="28"/>
       <c r="C4" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
@@ -964,13 +959,11 @@
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="28"/>
-      <c r="B5" s="4" t="s">
-        <v>3</v>
-      </c>
+    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="33"/>
+      <c r="B5" s="29"/>
       <c r="C5" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -988,15 +981,15 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
     </row>
-    <row r="6" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
+    <row r="6" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -1014,13 +1007,11 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
-      <c r="B7" s="8" t="s">
-        <v>8</v>
-      </c>
+    <row r="7" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="32"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
@@ -1038,13 +1029,11 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="26"/>
-      <c r="B8" s="4" t="s">
-        <v>8</v>
-      </c>
+    <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="32"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
@@ -1062,13 +1051,13 @@
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
     </row>
-    <row r="9" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
+    <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="32"/>
+      <c r="B9" s="27" t="s">
+        <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -1086,13 +1075,11 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
-      <c r="B10" s="8" t="s">
-        <v>9</v>
-      </c>
+    <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="32"/>
+      <c r="B10" s="28"/>
       <c r="C10" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
@@ -1110,13 +1097,11 @@
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="26"/>
-      <c r="B11" s="4" t="s">
-        <v>9</v>
-      </c>
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="32"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -1134,13 +1119,13 @@
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
     </row>
-    <row r="12" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26"/>
-      <c r="B12" s="2" t="s">
-        <v>10</v>
+    <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="32"/>
+      <c r="B12" s="27" t="s">
+        <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -1158,13 +1143,11 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="26"/>
-      <c r="B13" s="8" t="s">
-        <v>10</v>
-      </c>
+    <row r="13" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="32"/>
+      <c r="B13" s="28"/>
       <c r="C13" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
@@ -1182,13 +1165,11 @@
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
-      <c r="B14" s="4" t="s">
-        <v>10</v>
-      </c>
+    <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="33"/>
+      <c r="B14" s="29"/>
       <c r="C14" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
@@ -1206,15 +1187,15 @@
       <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
     </row>
-    <row r="15" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>12</v>
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -1232,13 +1213,11 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="8" t="s">
-        <v>12</v>
-      </c>
+    <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="32"/>
+      <c r="B16" s="28"/>
       <c r="C16" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
@@ -1256,13 +1235,11 @@
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
-      <c r="B17" s="4" t="s">
-        <v>12</v>
-      </c>
+    <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="32"/>
+      <c r="B17" s="29"/>
       <c r="C17" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -1280,13 +1257,13 @@
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="2" t="s">
-        <v>13</v>
+    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="32"/>
+      <c r="B18" s="27" t="s">
+        <v>28</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -1304,13 +1281,11 @@
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="8" t="s">
-        <v>13</v>
-      </c>
+    <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="32"/>
+      <c r="B19" s="28"/>
       <c r="C19" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -1328,13 +1303,11 @@
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
-      <c r="B20" s="4" t="s">
-        <v>13</v>
-      </c>
+    <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="32"/>
+      <c r="B20" s="29"/>
       <c r="C20" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -1352,13 +1325,13 @@
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="2" t="s">
-        <v>14</v>
+    <row r="21" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="32"/>
+      <c r="B21" s="27" t="s">
+        <v>29</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -1376,13 +1349,11 @@
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="26"/>
-      <c r="B22" s="8" t="s">
-        <v>14</v>
-      </c>
+    <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="32"/>
+      <c r="B22" s="28"/>
       <c r="C22" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -1400,13 +1371,11 @@
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
-      <c r="B23" s="4" t="s">
-        <v>14</v>
-      </c>
+    <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="33"/>
+      <c r="B23" s="29"/>
       <c r="C23" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
@@ -1424,15 +1393,15 @@
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
     </row>
-    <row r="24" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>16</v>
+    <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>31</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -1450,13 +1419,11 @@
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" s="26"/>
-      <c r="B25" s="8" t="s">
-        <v>16</v>
-      </c>
+    <row r="25" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="32"/>
+      <c r="B25" s="28"/>
       <c r="C25" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -1474,13 +1441,11 @@
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" s="26"/>
-      <c r="B26" s="4" t="s">
-        <v>16</v>
-      </c>
+    <row r="26" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="32"/>
+      <c r="B26" s="29"/>
       <c r="C26" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -1498,13 +1463,13 @@
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A27" s="26"/>
-      <c r="B27" s="2" t="s">
-        <v>17</v>
+    <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="32"/>
+      <c r="B27" s="27" t="s">
+        <v>32</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -1522,13 +1487,11 @@
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" s="26"/>
-      <c r="B28" s="8" t="s">
-        <v>17</v>
-      </c>
+    <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="32"/>
+      <c r="B28" s="28"/>
       <c r="C28" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
@@ -1546,13 +1509,11 @@
       <c r="Q28" s="7"/>
       <c r="R28" s="7"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" s="26"/>
-      <c r="B29" s="4" t="s">
-        <v>17</v>
-      </c>
+    <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="32"/>
+      <c r="B29" s="29"/>
       <c r="C29" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
@@ -1570,13 +1531,13 @@
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
     </row>
-    <row r="30" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
-      <c r="B30" s="2" t="s">
-        <v>18</v>
+    <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="32"/>
+      <c r="B30" s="27" t="s">
+        <v>33</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -1594,13 +1555,11 @@
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" s="26"/>
-      <c r="B31" s="8" t="s">
-        <v>18</v>
-      </c>
+    <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="32"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
@@ -1618,13 +1577,11 @@
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" s="28"/>
-      <c r="B32" s="4" t="s">
-        <v>18</v>
-      </c>
+    <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="33"/>
+      <c r="B32" s="29"/>
       <c r="C32" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
@@ -1642,59 +1599,69 @@
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
     </row>
-    <row r="33" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33"/>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="33"/>
-    </row>
-    <row r="34" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="36"/>
-      <c r="N34" s="36"/>
-      <c r="O34" s="36"/>
-      <c r="P34" s="36"/>
-      <c r="Q34" s="36"/>
-      <c r="R34" s="36"/>
+    <row r="33" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="26"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="26"/>
+    </row>
+    <row r="34" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="25"/>
+      <c r="O34" s="25"/>
+      <c r="P34" s="25"/>
+      <c r="Q34" s="25"/>
+      <c r="R34" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A34:C34"/>
+  <mergeCells count="17">
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B30:B32"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A14"/>
     <mergeCell ref="A15:A23"/>
     <mergeCell ref="A24:A32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B20"/>
   </mergeCells>
   <conditionalFormatting sqref="D3:R3">
     <cfRule type="top10" dxfId="13" priority="10" bottom="1" rank="1"/>
@@ -1733,82 +1700,82 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.109375" customWidth="1"/>
-    <col min="2" max="9" width="15.109375" customWidth="1"/>
-    <col min="10" max="15" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="8.140625" customWidth="1"/>
+    <col min="2" max="9" width="15.140625" customWidth="1"/>
+    <col min="10" max="15" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="C2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="I2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="J2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="K2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="L2" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="M2" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="N2" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="O2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1825,9 +1792,9 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1844,9 +1811,9 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1863,9 +1830,9 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -1882,9 +1849,9 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1901,9 +1868,9 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1920,9 +1887,9 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1939,9 +1906,9 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1958,9 +1925,9 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -1977,9 +1944,9 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -2012,82 +1979,82 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="9" width="15.109375" customWidth="1"/>
-    <col min="10" max="15" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="9" width="15.140625" customWidth="1"/>
+    <col min="10" max="15" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="I2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="J2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="K2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="L2" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="M2" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="N2" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="O2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -2104,9 +2071,9 @@
       <c r="N3" s="13"/>
       <c r="O3" s="13"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -2123,9 +2090,9 @@
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -2142,9 +2109,9 @@
       <c r="N5" s="14"/>
       <c r="O5" s="14"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
@@ -2161,9 +2128,9 @@
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
@@ -2180,9 +2147,9 @@
       <c r="N7" s="14"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
@@ -2199,9 +2166,9 @@
       <c r="N8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
@@ -2218,9 +2185,9 @@
       <c r="N9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -2237,9 +2204,9 @@
       <c r="N10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -2256,9 +2223,9 @@
       <c r="N11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -2291,82 +2258,82 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="9" width="15.109375" customWidth="1"/>
-    <col min="10" max="15" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="9" width="15.140625" customWidth="1"/>
+    <col min="10" max="15" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="I2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="J2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="K2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="L2" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="M2" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="N2" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="O2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -2383,9 +2350,9 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2402,9 +2369,9 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2421,9 +2388,9 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -2440,9 +2407,9 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -2459,9 +2426,9 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -2478,9 +2445,9 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -2497,9 +2464,9 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -2516,9 +2483,9 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -2535,9 +2502,9 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -2570,82 +2537,82 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="9" width="15.109375" customWidth="1"/>
-    <col min="10" max="15" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="9" width="15.140625" customWidth="1"/>
+    <col min="10" max="15" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="I2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="J2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="K2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="L2" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="M2" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="N2" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="O2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -2662,9 +2629,9 @@
       <c r="N3" s="13"/>
       <c r="O3" s="13"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -2681,9 +2648,9 @@
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -2700,9 +2667,9 @@
       <c r="N5" s="14"/>
       <c r="O5" s="14"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
@@ -2719,9 +2686,9 @@
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
@@ -2738,9 +2705,9 @@
       <c r="N7" s="14"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
@@ -2757,9 +2724,9 @@
       <c r="N8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
@@ -2776,9 +2743,9 @@
       <c r="N9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -2795,9 +2762,9 @@
       <c r="N10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -2814,9 +2781,9 @@
       <c r="N11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -2849,83 +2816,83 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="6" customWidth="1"/>
-    <col min="2" max="9" width="15.109375" style="6" customWidth="1"/>
-    <col min="10" max="15" width="16.109375" style="6" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="8.7109375" style="6" customWidth="1"/>
+    <col min="2" max="9" width="15.140625" style="6" customWidth="1"/>
+    <col min="10" max="15" width="16.140625" style="6" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="I2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="J2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="K2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="L2" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="M2" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="N2" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="O2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2942,9 +2909,9 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2961,9 +2928,9 @@
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2980,9 +2947,9 @@
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2999,9 +2966,9 @@
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -3018,9 +2985,9 @@
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -3037,9 +3004,9 @@
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -3056,9 +3023,9 @@
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -3075,9 +3042,9 @@
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -3094,9 +3061,9 @@
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -3124,100 +3091,102 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:S25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="D2" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="E2" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="F2" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="G2" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="H2" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="I2" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="J2" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="K2" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="L2" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="M2" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="N2" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="O2" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="P2" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="Q2" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="R2" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="S2" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="R2" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="S2" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -3238,9 +3207,9 @@
       <c r="R3" s="17"/>
       <c r="S3" s="17"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -3261,9 +3230,9 @@
       <c r="R4" s="17"/>
       <c r="S4" s="17"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -3284,9 +3253,9 @@
       <c r="R5" s="17"/>
       <c r="S5" s="17"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -3307,9 +3276,9 @@
       <c r="R6" s="17"/>
       <c r="S6" s="17"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -3330,9 +3299,9 @@
       <c r="R7" s="17"/>
       <c r="S7" s="17"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -3353,9 +3322,9 @@
       <c r="R8" s="17"/>
       <c r="S8" s="17"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -3376,9 +3345,9 @@
       <c r="R9" s="17"/>
       <c r="S9" s="17"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -3399,9 +3368,9 @@
       <c r="R10" s="17"/>
       <c r="S10" s="17"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
@@ -3422,9 +3391,9 @@
       <c r="R11" s="17"/>
       <c r="S11" s="17"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -3445,7 +3414,7 @@
       <c r="R12" s="17"/>
       <c r="S12" s="17"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -3466,53 +3435,53 @@
       <c r="R13" s="17"/>
       <c r="S13" s="17"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="19"/>
-      <c r="S14" s="19"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="20"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="18"/>
+      <c r="S14" s="18"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -3533,32 +3502,32 @@
       <c r="R16" s="17"/>
       <c r="S16" s="17"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>76</v>
-      </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="21"/>
-      <c r="S17" s="21"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
-        <v>77</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -3579,9 +3548,9 @@
       <c r="R18" s="17"/>
       <c r="S18" s="17"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -3602,9 +3571,9 @@
       <c r="R19" s="17"/>
       <c r="S19" s="17"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -3625,7 +3594,7 @@
       <c r="R20" s="17"/>
       <c r="S20" s="17"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -3646,18 +3615,18 @@
       <c r="R21" s="17"/>
       <c r="S21" s="17"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A22" s="21" t="s">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="C22" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="20" t="s">
         <v>80</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
@@ -3675,7 +3644,7 @@
       <c r="R22" s="17"/>
       <c r="S22" s="17"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -3696,7 +3665,7 @@
       <c r="R23" s="17"/>
       <c r="S23" s="17"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -3717,7 +3686,7 @@
       <c r="R24" s="17"/>
       <c r="S24" s="17"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -3739,6 +3708,9 @@
       <c r="S25" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:S1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3746,82 +3718,82 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="23" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="B2" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="23" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
+      <c r="B3" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="23" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="B4" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="23" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+      <c r="B5" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="23" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+      <c r="B6" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="23" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+      <c r="B7" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="23" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="B8" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="B8" s="23" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
+      <c r="B9" s="24" t="s">
         <v>98</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>99</v>
       </c>
     </row>
   </sheetData>
